--- a/data/playin2025/tpbl_summary.xlsx
+++ b/data/playin2025/tpbl_summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F65E56-F4F3-432A-A9A7-9F239FAE83E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED3D75C-D2E9-430E-8C0B-11601896FA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
   <si>
     <t xml:space="preserve">2025-2026 賽季 TPBL 季後挑戰賽 7隊戰力與綜合評分總表 </t>
   </si>
@@ -1081,7 +1081,9 @@
       <c r="A17" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="10"/>
+      <c r="B17" s="10" t="s">
+        <v>17</v>
+      </c>
       <c r="C17" s="14" t="s">
         <v>48</v>
       </c>
@@ -1105,7 +1107,9 @@
       <c r="A19" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="10"/>
+      <c r="B19" s="10" t="s">
+        <v>24</v>
+      </c>
       <c r="C19" t="s">
         <v>52</v>
       </c>

--- a/data/playin2025/tpbl_summary.xlsx
+++ b/data/playin2025/tpbl_summary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED3D75C-D2E9-430E-8C0B-11601896FA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF246D88-F962-4937-BC0F-3F8EF7439988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,10 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
-  <si>
-    <t xml:space="preserve">2025-2026 賽季 TPBL 季後挑戰賽 7隊戰力與綜合評分總表 </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>【區塊 A：團隊四大要素與進階數據指標 (Team Four Factors &amp; Advanced Metrics)】</t>
   </si>
@@ -68,9 +65,6 @@
     <t>團隊失誤率 (Team TOV%)</t>
   </si>
   <si>
-    <t>福爾摩沙夢想家</t>
-  </si>
-  <si>
     <t>新北國王</t>
   </si>
   <si>
@@ -89,9 +83,6 @@
     <t>14.0%</t>
   </si>
   <si>
-    <t>高雄全家海神</t>
-  </si>
-  <si>
     <t>新北中信特攻</t>
   </si>
   <si>
@@ -110,15 +101,6 @@
     <t>13.8%</t>
   </si>
   <si>
-    <t>臺北台新戰神</t>
-  </si>
-  <si>
-    <t>桃園台啤永豐雲豹</t>
-  </si>
-  <si>
-    <t>新竹御嵿攻城獅</t>
-  </si>
-  <si>
     <t>【區塊 B：重點球員洞察與戰力短評 (Player Insights &amp; Team Evaluation)】</t>
   </si>
   <si>
@@ -183,6 +165,9 @@
   </si>
   <si>
     <t>謝亞軒 (GmSc 13.0, eFG% 63.5%)、飛克 (GmSc 11.7, eFG% 50.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-2026 賽季 TPBL 季後挑戰賽 2隊戰力與綜合評分總表 </t>
   </si>
 </sst>
 </file>
@@ -531,7 +516,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A6:M12" headerRowCount="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A6:M7" headerRowCount="0">
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2"/>
@@ -552,7 +537,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A16:E22" headerRowCount="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A11:E12" headerRowCount="0">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Column2"/>
@@ -765,7 +750,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5546875" customWidth="1"/>
@@ -785,7 +770,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="6" t="s">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -818,7 +803,7 @@
     <row r="3" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="15" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -835,322 +820,188 @@
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="I5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="J5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="K5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="L5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="M5" s="9" t="s">
         <v>13</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="10">
+        <v>2</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="12"/>
+      <c r="D6" s="11">
+        <v>480</v>
+      </c>
+      <c r="E6" s="11">
+        <v>198</v>
+      </c>
+      <c r="F6" s="11">
+        <v>157</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="11">
+        <v>178.9</v>
+      </c>
+      <c r="K6" s="11">
+        <v>89.5</v>
+      </c>
+      <c r="L6" s="11">
+        <v>110.7</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="7" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B7" s="10">
         <v>2</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D7" s="11">
         <v>480</v>
       </c>
       <c r="E7" s="11">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F7" s="11">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="11">
+        <v>180.5</v>
+      </c>
+      <c r="K7" s="11">
+        <v>90.2</v>
+      </c>
+      <c r="L7" s="11">
+        <v>97.5</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="17"/>
+    </row>
+    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="132" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="118.8" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="11">
-        <v>178.9</v>
-      </c>
-      <c r="K7" s="11">
-        <v>89.5</v>
-      </c>
-      <c r="L7" s="11">
-        <v>110.7</v>
-      </c>
-      <c r="M7" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="12"/>
-    </row>
-    <row r="9" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="10">
-        <v>2</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="11">
-        <v>480</v>
-      </c>
-      <c r="E9" s="11">
-        <v>176</v>
-      </c>
-      <c r="F9" s="11">
-        <v>167</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="11">
-        <v>180.5</v>
-      </c>
-      <c r="K9" s="11">
-        <v>90.2</v>
-      </c>
-      <c r="L9" s="11">
-        <v>97.5</v>
-      </c>
-      <c r="M9" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="12"/>
-    </row>
-    <row r="11" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="12"/>
-    </row>
-    <row r="12" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="12"/>
-    </row>
-    <row r="13" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17"/>
-    </row>
-    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-    </row>
-    <row r="17" spans="1:5" ht="132" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-    </row>
-    <row r="19" spans="1:5" ht="118.8" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-    </row>
-    <row r="21" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-    </row>
-    <row r="22" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
@@ -1176,36 +1027,36 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
@@ -1213,7 +1064,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
@@ -1221,7 +1072,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="5"/>
@@ -1229,7 +1080,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="5"/>
